--- a/data/trans_camb/P20B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P20B-Edad-trans_camb.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 32,22</t>
+          <t>-36,77; 38,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 32,32</t>
+          <t>-43,65; 32,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 20,81</t>
+          <t>-2,66; 23,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 17,73</t>
+          <t>-6,45; 17,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 55,68</t>
+          <t>-5,88; 50,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 22,11</t>
+          <t>-6,99; 22,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 15,9</t>
+          <t>-11,23; 15,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 39,7</t>
+          <t>-14,44; 41,23</t>
         </is>
       </c>
     </row>
@@ -783,42 +783,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-74,29; —</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,37; 732,72</t>
+          <t>-52,47; 601,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,78; 533,41</t>
+          <t>-77,95; 543,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-29,83; 14,97</t>
+          <t>-28,17; 15,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 17,6</t>
+          <t>-35,28; 13,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 49,15</t>
+          <t>-27,23; 46,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 5,45</t>
+          <t>-10,62; 5,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 8,24</t>
+          <t>-8,3; 8,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 13,38</t>
+          <t>-9,56; 17,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 4,79</t>
+          <t>-12,26; 4,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 5,04</t>
+          <t>-12,58; 6,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 18,02</t>
+          <t>-8,91; 18,29</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,35; 162,94</t>
+          <t>-77,9; 155,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 244,1</t>
+          <t>-100,0; 172,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 416,9</t>
+          <t>-100,0; 352,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-81,28; 210,38</t>
+          <t>-86,66; 202,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,55; 211,84</t>
+          <t>-76,83; 281,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 376,04</t>
+          <t>-100,0; 1061,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 68,15</t>
+          <t>-71,39; 72,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,06; 77,53</t>
+          <t>-73,07; 102,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-69,6; 242,78</t>
+          <t>-63,26; 237,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-34,85; 20,11</t>
+          <t>-33,14; 22,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 39,36</t>
+          <t>-26,11; 35,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-43,75; 16,14</t>
+          <t>-46,27; 12,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 31,5</t>
+          <t>-6,93; 30,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 13,97</t>
+          <t>-18,38; 15,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 21,65</t>
+          <t>-13,79; 20,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 20,95</t>
+          <t>-10,93; 21,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 14,45</t>
+          <t>-17,08; 14,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 11,96</t>
+          <t>-17,91; 12,03</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-61,93; 107,38</t>
+          <t>-63,01; 119,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 203,0</t>
+          <t>-48,71; 182,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,51; 75,82</t>
+          <t>-83,24; 72,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 353,7</t>
+          <t>-24,07; 326,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,81; 170,25</t>
+          <t>-68,71; 202,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 234,75</t>
+          <t>-51,06; 200,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 125,09</t>
+          <t>-31,99; 125,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,78; 86,07</t>
+          <t>-49,56; 86,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,3; 72,4</t>
+          <t>-53,2; 71,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 46,13</t>
+          <t>-1,3; 45,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 50,89</t>
+          <t>-0,26; 53,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 42,35</t>
+          <t>-0,65; 41,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 33,03</t>
+          <t>-11,86; 34,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 33,48</t>
+          <t>-18,25; 34,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 28,15</t>
+          <t>-19,35; 27,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 34,5</t>
+          <t>1,96; 35,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 34,29</t>
+          <t>-2,58; 35,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 28,83</t>
+          <t>-9,63; 26,33</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 839,03</t>
+          <t>-10,56; 885,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 971,47</t>
+          <t>-19,96; 817,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 780,14</t>
+          <t>-7,87; 814,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,81; 141,96</t>
+          <t>-23,97; 148,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 148,94</t>
+          <t>-37,41; 152,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 129,25</t>
+          <t>-35,7; 124,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 188,04</t>
+          <t>3,74; 197,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 185,35</t>
+          <t>-6,94; 192,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 157,43</t>
+          <t>-23,6; 141,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-40,19; 17,33</t>
+          <t>-38,4; 20,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-25,4; 31,49</t>
+          <t>-27,39; 31,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 16,2</t>
+          <t>-34,92; 15,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 16,37</t>
+          <t>-33,98; 17,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 28,7</t>
+          <t>-27,2; 29,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 3,54</t>
+          <t>-43,57; 4,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-31,77; 8,69</t>
+          <t>-29,19; 11,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 20,11</t>
+          <t>-16,77; 21,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 4,99</t>
+          <t>-29,86; 4,16</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,78; 68,0</t>
+          <t>-65,99; 81,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,68; 116,81</t>
+          <t>-48,43; 119,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,5; 66,97</t>
+          <t>-56,44; 52,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-59,14; 49,87</t>
+          <t>-56,24; 56,47</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,59; 87,43</t>
+          <t>-45,65; 91,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,18; 13,65</t>
+          <t>-69,16; 18,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 24,37</t>
+          <t>-51,06; 33,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 57,98</t>
+          <t>-29,68; 58,59</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-52,96; 15,78</t>
+          <t>-52,77; 12,95</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 36,78</t>
+          <t>-12,87; 35,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 22,46</t>
+          <t>-23,07; 21,35</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 38,34</t>
+          <t>-5,22; 38,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 22,45</t>
+          <t>-24,98; 22,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 36,26</t>
+          <t>-14,77; 37,39</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 7,16</t>
+          <t>-33,83; 6,87</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 21,29</t>
+          <t>-11,12; 22,79</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 21,83</t>
+          <t>-10,7; 21,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 19,3</t>
+          <t>-11,2; 19,5</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-52,5; 368,79</t>
+          <t>-43,38; 443,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-65,6; 240,9</t>
+          <t>-67,2; 258,04</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 451,67</t>
+          <t>-18,02; 451,64</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 106,26</t>
+          <t>-54,92; 108,54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-31,99; 166,84</t>
+          <t>-36,88; 172,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-71,4; 34,11</t>
+          <t>-72,04; 44,07</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 105,96</t>
+          <t>-30,32; 122,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 109,19</t>
+          <t>-31,42; 122,09</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-29,83; 95,54</t>
+          <t>-29,88; 101,79</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 26,52</t>
+          <t>-16,22; 23,26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 36,13</t>
+          <t>-10,65; 34,41</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 21,73</t>
+          <t>-14,77; 22,33</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 13,54</t>
+          <t>-19,79; 14,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 30,92</t>
+          <t>-11,03; 29,8</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 22,67</t>
+          <t>-11,45; 21,64</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 13,36</t>
+          <t>-11,73; 13,89</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 26,18</t>
+          <t>-4,83; 25,47</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 17,98</t>
+          <t>-6,66; 18,31</t>
         </is>
       </c>
     </row>
@@ -2084,42 +2084,42 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-60,64; —</t>
+          <t>-58,19; 902,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-63,38; 483,47</t>
+          <t>-59,33; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-77,38; 192,3</t>
+          <t>-73,71; 219,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-42,24; 525,17</t>
+          <t>-50,37; 406,61</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 340,88</t>
+          <t>-41,25; 303,85</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-58,23; 182,22</t>
+          <t>-55,1; 167,61</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,48; 298,42</t>
+          <t>-29,16; 316,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 220,1</t>
+          <t>-28,3; 257,91</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 13,26</t>
+          <t>-5,92; 13,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 17,68</t>
+          <t>-3,07; 17,54</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 16,72</t>
+          <t>-3,62; 16,01</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 11,25</t>
+          <t>-2,65; 11,62</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 11,06</t>
+          <t>-3,43; 12,17</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 9,37</t>
+          <t>-4,76; 9,78</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 9,97</t>
+          <t>-1,67; 10,1</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 11,73</t>
+          <t>-0,33; 11,75</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 11,33</t>
+          <t>-0,51; 11,17</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 62,52</t>
+          <t>-18,78; 65,53</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 80,31</t>
+          <t>-9,57; 86,94</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 85,3</t>
+          <t>-11,65; 75,41</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 71,67</t>
+          <t>-11,54; 68,51</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 67,62</t>
+          <t>-15,11; 75,03</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 56,77</t>
+          <t>-19,19; 58,48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 50,26</t>
+          <t>-6,46; 52,8</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 60,56</t>
+          <t>-0,99; 61,44</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 58,96</t>
+          <t>-2,09; 57,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P20B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P20B-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,38</t>
+          <t>10,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>3,19</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-36,77; 38,64</t>
+          <t>-39,62; 35,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-43,65; 32,99</t>
+          <t>-43,58; 33,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 23,13</t>
+          <t>-3,71; 21,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 17,82</t>
+          <t>-6,3; 16,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 50,99</t>
+          <t>-6,24; 51,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 22,93</t>
+          <t>-7,81; 20,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 15,68</t>
+          <t>-11,49; 16,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 41,23</t>
+          <t>-13,06; 35,97</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>357,35%</t>
+          <t>334,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -783,42 +783,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,29; —</t>
+          <t>-80,16; 476,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 440,12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 601,87</t>
+          <t>-51,44; 663,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,95; 543,6</t>
+          <t>-75,87; 565,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,11</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 15,77</t>
+          <t>-29,19; 14,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-35,28; 13,72</t>
+          <t>-35,66; 15,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 46,45</t>
+          <t>-26,71; 43,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 5,18</t>
+          <t>-10,54; 4,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 8,84</t>
+          <t>-8,67; 9,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 17,25</t>
+          <t>-10,52; 12,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 4,87</t>
+          <t>-11,21; 5,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 6,16</t>
+          <t>-12,22; 6,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 18,29</t>
+          <t>-9,46; 16,35</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-9,9%</t>
+          <t>-17,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,9; 155,67</t>
+          <t>-79,99; 133,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 172,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 352,76</t>
+          <t>-100,0; 379,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-86,66; 202,41</t>
+          <t>-80,43; 194,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,83; 281,04</t>
+          <t>-78,05; 258,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1061,56</t>
+          <t>-100,0; 486,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,39; 72,63</t>
+          <t>-68,33; 75,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,07; 102,52</t>
+          <t>-74,03; 90,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,26; 237,95</t>
+          <t>-68,33; 192,97</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-14,68</t>
+          <t>-13,18</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-2,47</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 22,45</t>
+          <t>-35,07; 22,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 35,96</t>
+          <t>-24,74; 37,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-46,27; 12,91</t>
+          <t>-41,65; 16,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 30,2</t>
+          <t>-5,4; 29,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 15,58</t>
+          <t>-20,56; 12,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 20,03</t>
+          <t>-13,48; 18,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 21,4</t>
+          <t>-9,17; 22,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 14,54</t>
+          <t>-15,91; 14,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 12,03</t>
+          <t>-19,35; 11,73</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-38,59%</t>
+          <t>-34,64%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-8,88%</t>
+          <t>-9,8%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,01; 119,52</t>
+          <t>-63,72; 111,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,71; 182,89</t>
+          <t>-45,1; 201,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-83,24; 72,69</t>
+          <t>-79,47; 106,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 326,04</t>
+          <t>-23,53; 362,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,71; 202,1</t>
+          <t>-76,28; 134,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 200,17</t>
+          <t>-52,89; 188,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,99; 125,87</t>
+          <t>-25,59; 146,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 86,61</t>
+          <t>-48,44; 83,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 71,71</t>
+          <t>-56,32; 68,16</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20,96</t>
+          <t>24,56</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>6,32</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,95</t>
+          <t>14,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 45,84</t>
+          <t>2,95; 48,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 53,34</t>
+          <t>0,37; 53,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 41,5</t>
+          <t>2,17; 47,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 34,57</t>
+          <t>-11,93; 36,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 34,67</t>
+          <t>-15,67; 35,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 27,48</t>
+          <t>-18,32; 27,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 35,55</t>
+          <t>2,34; 35,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 35,14</t>
+          <t>-2,58; 35,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 26,33</t>
+          <t>-3,17; 30,77</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123,09%</t>
+          <t>144,22%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 885,29</t>
+          <t>-0,32; 974,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 817,66</t>
+          <t>-13,93; 823,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 814,4</t>
+          <t>-6,26; 911,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 148,94</t>
+          <t>-23,69; 163,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,41; 152,91</t>
+          <t>-33,23; 154,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 124,85</t>
+          <t>-33,92; 114,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,74; 197,33</t>
+          <t>4,87; 196,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 192,27</t>
+          <t>-7,22; 185,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 141,42</t>
+          <t>-9,23; 171,57</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-8,25</t>
+          <t>-9,56</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-18,69</t>
+          <t>-15,29</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-12,76</t>
+          <t>-12,3</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-38,4; 20,3</t>
+          <t>-39,52; 16,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 31,58</t>
+          <t>-26,68; 30,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 15,71</t>
+          <t>-36,51; 14,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 17,62</t>
+          <t>-31,92; 21,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 29,11</t>
+          <t>-26,19; 31,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-43,57; 4,35</t>
+          <t>-38,78; 8,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 11,72</t>
+          <t>-27,89; 9,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 21,1</t>
+          <t>-18,71; 23,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-29,86; 4,16</t>
+          <t>-29,25; 4,67</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-18,23%</t>
+          <t>-21,12%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-39,11%</t>
+          <t>-31,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-27,31%</t>
+          <t>-26,33%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,99; 81,22</t>
+          <t>-66,21; 55,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,43; 119,84</t>
+          <t>-44,18; 123,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 52,97</t>
+          <t>-56,76; 61,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-56,24; 56,47</t>
+          <t>-55,15; 75,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 91,08</t>
+          <t>-45,64; 100,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,16; 18,15</t>
+          <t>-63,67; 28,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 33,11</t>
+          <t>-49,93; 29,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 58,59</t>
+          <t>-31,55; 65,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-52,77; 12,95</t>
+          <t>-49,79; 15,15</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19,63</t>
+          <t>18,31</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-12,66</t>
+          <t>-12,45</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>3,99</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 35,93</t>
+          <t>-14,15; 36,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 21,35</t>
+          <t>-22,36; 23,08</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 38,61</t>
+          <t>-4,74; 37,54</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 22,87</t>
+          <t>-25,53; 21,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 37,39</t>
+          <t>-13,35; 36,78</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 6,87</t>
+          <t>-31,37; 8,98</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 22,79</t>
+          <t>-13,12; 21,37</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 21,8</t>
+          <t>-11,49; 21,18</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 19,5</t>
+          <t>-10,94; 18,12</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-37,35%</t>
+          <t>-36,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-43,38; 443,67</t>
+          <t>-44,39; 419,55</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-67,2; 258,04</t>
+          <t>-62,88; 259,69</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 451,64</t>
+          <t>-15,59; 409,1</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-54,92; 108,54</t>
+          <t>-54,29; 103,36</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 172,79</t>
+          <t>-33,39; 180,91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-72,04; 44,07</t>
+          <t>-69,95; 50,17</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-30,32; 122,97</t>
+          <t>-35,66; 105,95</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 122,09</t>
+          <t>-33,16; 108,92</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 101,79</t>
+          <t>-30,82; 99,04</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>6,55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,53</t>
+          <t>8,82</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,84</t>
+          <t>7,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 23,26</t>
+          <t>-18,12; 24,03</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 34,41</t>
+          <t>-10,24; 34,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 22,33</t>
+          <t>-14,94; 22,91</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 14,71</t>
+          <t>-19,74; 14,33</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 29,8</t>
+          <t>-7,89; 34,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 21,64</t>
+          <t>-11,37; 23,77</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 13,89</t>
+          <t>-13,68; 13,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 25,47</t>
+          <t>-5,12; 27,1</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 18,31</t>
+          <t>-5,34; 19,3</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>-82,67; —</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-58,19; 902,83</t>
-        </is>
-      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-59,33; —</t>
+          <t>-61,07; 513,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-73,71; 219,29</t>
+          <t>-75,08; 244,55</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,37; 406,61</t>
+          <t>-37,08; 506,31</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-41,25; 303,85</t>
+          <t>-38,19; 362,84</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-55,1; 167,61</t>
+          <t>-61,63; 170,54</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 316,9</t>
+          <t>-29,15; 326,2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 257,91</t>
+          <t>-23,86; 242,12</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,53</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 13,3</t>
+          <t>-6,01; 12,69</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 17,54</t>
+          <t>-2,92; 18,37</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 16,01</t>
+          <t>-3,1; 16,72</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 11,62</t>
+          <t>-2,61; 11,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 12,17</t>
+          <t>-3,2; 12,1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 9,78</t>
+          <t>-3,81; 10,36</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 10,1</t>
+          <t>-1,04; 9,68</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 11,75</t>
+          <t>-0,07; 12,17</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 11,17</t>
+          <t>-0,26; 11,18</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 65,53</t>
+          <t>-19,25; 59,09</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 86,94</t>
+          <t>-11,49; 83,04</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 75,41</t>
+          <t>-9,11; 84,18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 68,51</t>
+          <t>-11,73; 70,51</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 75,03</t>
+          <t>-14,13; 72,99</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 58,48</t>
+          <t>-14,98; 61,09</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 52,8</t>
+          <t>-4,21; 50,41</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 61,44</t>
+          <t>-0,56; 63,27</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 57,33</t>
+          <t>-1,13; 56,77</t>
         </is>
       </c>
     </row>
